--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>71.20137633103457</v>
+        <v>11.57022365379312</v>
       </c>
       <c r="D2" t="n">
-        <v>75.33372596229985</v>
+        <v>12.24173046887373</v>
       </c>
       <c r="E2" t="n">
-        <v>10.70837106460492</v>
+        <v>1.7401102979983</v>
       </c>
       <c r="F2" t="n">
-        <v>21.20243892989822</v>
+        <v>3.44539632610846</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>65.01935656041981</v>
+        <v>10.56564544106822</v>
       </c>
       <c r="D3" t="n">
-        <v>65.60373297421125</v>
+        <v>10.66060660830933</v>
       </c>
       <c r="E3" t="n">
-        <v>10.70837106460492</v>
+        <v>1.7401102979983</v>
       </c>
       <c r="F3" t="n">
-        <v>21.20243892989822</v>
+        <v>3.44539632610846</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.12037445906531</v>
+        <v>6.844560849598113</v>
       </c>
       <c r="D4" t="n">
-        <v>44.0668283029004</v>
+        <v>7.160859599221316</v>
       </c>
       <c r="E4" t="n">
-        <v>10.70837106460492</v>
+        <v>1.7401102979983</v>
       </c>
       <c r="F4" t="n">
-        <v>21.20243892989822</v>
+        <v>3.44539632610846</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>63.10809115683048</v>
+        <v>10.25506481298495</v>
       </c>
       <c r="D5" t="n">
-        <v>16.51183342080179</v>
+        <v>2.68317293088029</v>
       </c>
       <c r="E5" t="n">
-        <v>10.70837106460492</v>
+        <v>1.7401102979983</v>
       </c>
       <c r="F5" t="n">
-        <v>21.20243892989822</v>
+        <v>3.44539632610846</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>74.34979694736747</v>
+        <v>12.08184200394721</v>
       </c>
       <c r="D6" t="n">
-        <v>29.7405454676015</v>
+        <v>4.832838638485244</v>
       </c>
       <c r="E6" t="n">
-        <v>10.70837106460492</v>
+        <v>1.7401102979983</v>
       </c>
       <c r="F6" t="n">
-        <v>21.20243892989822</v>
+        <v>3.44539632610846</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>71.06024708395756</v>
+        <v>11.5472901511431</v>
       </c>
       <c r="D7" t="n">
-        <v>26.80468209952747</v>
+        <v>4.355760841173214</v>
       </c>
       <c r="E7" t="n">
-        <v>10.70837106460492</v>
+        <v>1.7401102979983</v>
       </c>
       <c r="F7" t="n">
-        <v>21.20243892989822</v>
+        <v>3.44539632610846</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
